--- a/create_forecast_basic/future/JTMT/Intermediates/240703_pop_2050_jtmt.xlsx
+++ b/create_forecast_basic/future/JTMT/Intermediates/240703_pop_2050_jtmt.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="n">
-        <v>1518.880760635146</v>
+        <v>1518.880760635145</v>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="n">
-        <v>4596.95529565095</v>
+        <v>4596.955295650952</v>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
-        <v>4064.435855247981</v>
+        <v>4064.435855247984</v>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>18734.84936780013</v>
+        <v>18734.84936780011</v>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="n">
-        <v>10625.40039917612</v>
+        <v>10625.40039917611</v>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
-        <v>18616.15539330787</v>
+        <v>18616.15539330788</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>50237.98144499646</v>
+        <v>50237.98144499648</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>37138.88477115368</v>
+        <v>37138.88477115364</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>11966.53104400984</v>
+        <v>11966.53104400985</v>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>1757.556404556162</v>
+        <v>1757.556404556163</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
-        <v>8611.030039720728</v>
+        <v>8611.03003972073</v>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>2716.742776104742</v>
+        <v>2716.742776104744</v>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>15523.23023790245</v>
+        <v>15523.23023790243</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
-        <v>3660.900832810687</v>
+        <v>3660.900832810684</v>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="n">
-        <v>9091.052877980699</v>
+        <v>9091.052877980683</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
-        <v>8386.590834296972</v>
+        <v>8386.590834296969</v>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
-        <v>45640.9662853259</v>
+        <v>45640.96628532591</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>12195.97182881198</v>
+        <v>12195.97182881199</v>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>15412.02546738571</v>
+        <v>15412.0254673857</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>33100.77510046069</v>
+        <v>33100.77510046071</v>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>7265.895619651596</v>
+        <v>7265.8956196516</v>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>6123.768482049434</v>
+        <v>6123.768482049433</v>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
-        <v>4805.434746091984</v>
+        <v>4805.434746091983</v>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="n">
-        <v>758.9941392370163</v>
+        <v>758.994139237016</v>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
-        <v>4333.429790695624</v>
+        <v>4333.429790695627</v>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="n">
-        <v>2851.52942663529</v>
+        <v>2851.529426635289</v>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
-        <v>4839.403224105657</v>
+        <v>4839.403224105658</v>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="n">
-        <v>8196.023825370923</v>
+        <v>8196.023825370921</v>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>4059.949525693156</v>
+        <v>4059.949525693158</v>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="n">
-        <v>3248.535602387202</v>
+        <v>3248.535602387201</v>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="n">
-        <v>5032.342877521954</v>
+        <v>5032.342877521955</v>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="n">
-        <v>5627.669030518975</v>
+        <v>5627.669030518974</v>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="n">
-        <v>6457.959038019636</v>
+        <v>6457.959038019638</v>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="n">
-        <v>9567.949671950097</v>
+        <v>9567.949671950093</v>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="n">
-        <v>6700.329642432981</v>
+        <v>6700.329642432979</v>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="n">
-        <v>67347.11080916658</v>
+        <v>67347.11080916662</v>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="n">
-        <v>58376.01370577871</v>
+        <v>58376.01370577869</v>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="n">
-        <v>61753.34437533776</v>
+        <v>61753.34437533773</v>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="n">
-        <v>80276.26303785456</v>
+        <v>80276.26303785457</v>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="n">
-        <v>100340.616782781</v>
+        <v>100340.6167827809</v>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="n">
-        <v>2078.456122337161</v>
+        <v>2078.456122337159</v>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="n">
-        <v>18706.51571220111</v>
+        <v>18706.5157122011</v>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="n">
-        <v>10789.31322816424</v>
+        <v>10789.31322816425</v>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
-        <v>4055.812628624863</v>
+        <v>4055.812628624862</v>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
-        <v>5365.973484845469</v>
+        <v>5365.973484845471</v>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
@@ -8264,7 +8264,7 @@
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="n">
-        <v>13657.89023430727</v>
+        <v>13657.89023430726</v>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="n">
-        <v>17643.89165186434</v>
+        <v>17643.89165186432</v>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="n">
-        <v>6363.389502865741</v>
+        <v>6363.389502865742</v>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="n">
-        <v>34524.42486474628</v>
+        <v>34524.42486474626</v>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="n">
-        <v>21267.41345431392</v>
+        <v>21267.41345431393</v>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="n">
-        <v>84011.00650073164</v>
+        <v>84011.00650073175</v>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="n">
-        <v>14140.89986242236</v>
+        <v>14140.89986242235</v>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="n">
-        <v>26407.46142611738</v>
+        <v>26407.46142611739</v>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="n">
-        <v>34039.29817542878</v>
+        <v>34039.29817542875</v>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="n">
-        <v>47635.52965129723</v>
+        <v>47635.52965129724</v>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr"/>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="n">
-        <v>9741.723575339665</v>
+        <v>9741.723575339667</v>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="n">
-        <v>7776.186947181794</v>
+        <v>7776.186947181792</v>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr"/>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="n">
-        <v>4189.780164398784</v>
+        <v>4189.780164398786</v>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr"/>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="n">
-        <v>4728.151750103202</v>
+        <v>4728.151750103203</v>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="n">
-        <v>5531.061235036696</v>
+        <v>5531.061235036695</v>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="n">
-        <v>14670.99298363003</v>
+        <v>14670.99298363001</v>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr"/>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="n">
-        <v>8562.423842440459</v>
+        <v>8562.423842440456</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr"/>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="n">
-        <v>51694.51309391279</v>
+        <v>51694.51309391278</v>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="n">
-        <v>53304.62795019934</v>
+        <v>53304.62795019933</v>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="n">
-        <v>36547.16885909747</v>
+        <v>36547.16885909746</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr"/>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="n">
-        <v>50546.06146141519</v>
+        <v>50546.06146141524</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr"/>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="n">
-        <v>37861.44872202112</v>
+        <v>37861.44872202111</v>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr"/>
